--- a/Data Analysis/1_Data/Aggregates/WSA_November_clean.xlsx
+++ b/Data Analysis/1_Data/Aggregates/WSA_November_clean.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aw52udov\Desktop\Masterarbeit\02_Methoden\03_WSA\01_RawData\03_November\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mm68tulo\Desktop\Jena Chapter\Data Analysis\1_Data\Aggregates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD03774B-4667-4EB1-879D-9259603FEA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E10FA1-C393-41A4-B6E6-1BA741480359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{BC0CCBAF-3D64-42AA-9871-21EBB1E9EF22}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BC0CCBAF-3D64-42AA-9871-21EBB1E9EF22}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle" sheetId="7" r:id="rId1"/>
@@ -36,9 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
-    <t>Plot/Subplot/Site</t>
-  </si>
-  <si>
     <t>B1A02</t>
   </si>
   <si>
@@ -108,9 +105,6 @@
     <t>SpeciesRichness</t>
   </si>
   <si>
-    <t>Mean_Overall_Aggregates</t>
-  </si>
-  <si>
     <t>Mean_WSA</t>
   </si>
   <si>
@@ -319,6 +313,12 @@
   </si>
   <si>
     <t>measured late</t>
+  </si>
+  <si>
+    <t>Plotcode</t>
+  </si>
+  <si>
+    <t>agg_overall</t>
   </si>
 </sst>
 </file>
@@ -455,7 +455,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -471,7 +471,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -768,54 +768,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2F59C97-A3F4-4299-9EF2-A3946D000391}">
   <dimension ref="A1:Q161"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="5" width="10.90625" style="9"/>
-    <col min="12" max="12" width="19.26953125" customWidth="1"/>
-    <col min="13" max="13" width="25.36328125" customWidth="1"/>
+    <col min="4" max="5" width="10.85546875" style="9"/>
+    <col min="12" max="12" width="19.28515625" customWidth="1"/>
+    <col min="13" max="13" width="25.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="K1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="B2" s="3">
         <v>87.1955462769657</v>
@@ -856,9 +856,9 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
     </row>
-    <row r="3" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="3">
         <v>89.340439706861957</v>
@@ -899,9 +899,9 @@
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
     </row>
-    <row r="4" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B4" s="3">
         <v>73.807829181494995</v>
@@ -942,9 +942,9 @@
       <c r="O4" s="12"/>
       <c r="P4" s="12"/>
     </row>
-    <row r="5" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B5" s="3">
         <v>68.066070199586903</v>
@@ -985,9 +985,9 @@
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
     </row>
-    <row r="6" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="3">
         <v>76.582709326072504</v>
@@ -1028,9 +1028,9 @@
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
     </row>
-    <row r="7" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3">
         <v>87.544232130219484</v>
@@ -1071,9 +1071,9 @@
       <c r="O7" s="12"/>
       <c r="P7" s="12"/>
     </row>
-    <row r="8" spans="1:16" ht="31" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:16" ht="30" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3">
         <v>74.665728360309586</v>
@@ -1109,15 +1109,15 @@
         <v>2.9213001233845128</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
     </row>
-    <row r="9" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" s="3">
         <v>74.811772758385075</v>
@@ -1158,9 +1158,9 @@
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
     </row>
-    <row r="10" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B10" s="3">
         <v>82.573179033356354</v>
@@ -1201,9 +1201,9 @@
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
     </row>
-    <row r="11" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B11" s="3">
         <v>69.336071184120428</v>
@@ -1244,9 +1244,9 @@
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
     </row>
-    <row r="12" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B12" s="3">
         <v>57.508196721311435</v>
@@ -1287,9 +1287,9 @@
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
     </row>
-    <row r="13" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="3">
         <v>82.820329277022282</v>
@@ -1330,9 +1330,9 @@
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
     </row>
-    <row r="14" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B14" s="3">
         <v>60.884125920964991</v>
@@ -1373,9 +1373,9 @@
       <c r="O14" s="12"/>
       <c r="P14" s="12"/>
     </row>
-    <row r="15" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B15" s="3">
         <v>70.622950819672056</v>
@@ -1416,9 +1416,9 @@
       <c r="O15" s="12"/>
       <c r="P15" s="12"/>
     </row>
-    <row r="16" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" s="3">
         <v>69.049180327868726</v>
@@ -1459,9 +1459,9 @@
       <c r="O16" s="12"/>
       <c r="P16" s="12"/>
     </row>
-    <row r="17" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B17" s="3">
         <v>76.582709326072333</v>
@@ -1502,9 +1502,9 @@
       <c r="O17" s="12"/>
       <c r="P17" s="12"/>
     </row>
-    <row r="18" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" s="3">
         <v>46.666666666666941</v>
@@ -1545,9 +1545,9 @@
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
     </row>
-    <row r="19" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B19" s="3">
         <v>85.851142225497682</v>
@@ -1588,9 +1588,9 @@
       <c r="O19" s="12"/>
       <c r="P19" s="12"/>
     </row>
-    <row r="20" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B20" s="3">
         <v>72.525252525252341</v>
@@ -1631,9 +1631,9 @@
       <c r="O20" s="12"/>
       <c r="P20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B21" s="3">
         <v>87.474472430225177</v>
@@ -1674,9 +1674,9 @@
       <c r="O21" s="12"/>
       <c r="P21" s="12"/>
     </row>
-    <row r="22" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B22" s="3">
         <v>87.60942760942801</v>
@@ -1717,9 +1717,9 @@
       <c r="O22" s="12"/>
       <c r="P22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B23" s="3">
         <v>79.417738659445078</v>
@@ -1760,9 +1760,9 @@
       <c r="O23" s="12"/>
       <c r="P23" s="12"/>
     </row>
-    <row r="24" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B24" s="3">
         <v>87.609427609427442</v>
@@ -1803,9 +1803,9 @@
       <c r="O24" s="12"/>
       <c r="P24" s="12"/>
     </row>
-    <row r="25" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" s="3">
         <v>64.399237126509817</v>
@@ -1846,9 +1846,9 @@
       <c r="O25" s="12"/>
       <c r="P25" s="12"/>
     </row>
-    <row r="26" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B26" s="3">
         <v>82.504970178926598</v>
@@ -1888,9 +1888,9 @@
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
     </row>
-    <row r="27" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B27" s="3">
         <v>85.609593604263395</v>
@@ -1931,9 +1931,9 @@
       <c r="O27" s="12"/>
       <c r="P27" s="12"/>
     </row>
-    <row r="28" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B28" s="3">
         <v>79.417738659445078</v>
@@ -1974,9 +1974,9 @@
       <c r="O28" s="12"/>
       <c r="P28" s="12"/>
     </row>
-    <row r="29" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29" s="3">
         <v>83.477681545636145</v>
@@ -2017,9 +2017,9 @@
       <c r="O29" s="12"/>
       <c r="P29" s="12"/>
     </row>
-    <row r="30" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B30" s="3">
         <v>91.426657736101973</v>
@@ -2060,9 +2060,9 @@
       <c r="O30" s="12"/>
       <c r="P30" s="12"/>
     </row>
-    <row r="31" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B31" s="3">
         <v>90.557377049179991</v>
@@ -2103,9 +2103,9 @@
       <c r="O31" s="12"/>
       <c r="P31" s="12"/>
     </row>
-    <row r="32" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B32" s="3">
         <v>79.647749510763262</v>
@@ -2146,9 +2146,9 @@
       <c r="O32" s="12"/>
       <c r="P32" s="12"/>
     </row>
-    <row r="33" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B33" s="3">
         <v>79.213857428381075</v>
@@ -2189,9 +2189,9 @@
       <c r="O33" s="12"/>
       <c r="P33" s="12"/>
     </row>
-    <row r="34" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B34" s="3">
         <v>63.027461486939117</v>
@@ -2232,9 +2232,9 @@
       <c r="O34" s="12"/>
       <c r="P34" s="12"/>
     </row>
-    <row r="35" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B35" s="3">
         <v>84.344422700587302</v>
@@ -2275,9 +2275,9 @@
       <c r="O35" s="12"/>
       <c r="P35" s="12"/>
     </row>
-    <row r="36" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B36" s="9">
         <v>86.571981923821582</v>
@@ -2318,9 +2318,9 @@
       <c r="O36" s="12"/>
       <c r="P36" s="12"/>
     </row>
-    <row r="37" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B37" s="3">
         <v>81.086261980830571</v>
@@ -2361,9 +2361,9 @@
       <c r="O37" s="12"/>
       <c r="P37" s="12"/>
     </row>
-    <row r="38" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B38" s="3">
         <v>83.213114754098001</v>
@@ -2404,9 +2404,9 @@
       <c r="O38" s="12"/>
       <c r="P38" s="12"/>
     </row>
-    <row r="39" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B39" s="4">
         <v>77.34424166142216</v>
@@ -2447,9 +2447,9 @@
       <c r="O39" s="12"/>
       <c r="P39" s="12"/>
     </row>
-    <row r="40" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B40" s="3">
         <v>83.477681545636145</v>
@@ -2490,9 +2490,9 @@
       <c r="O40" s="12"/>
       <c r="P40" s="12"/>
     </row>
-    <row r="41" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B41" s="3">
         <v>83.389149363697101</v>
@@ -2533,9 +2533,9 @@
       <c r="O41" s="12"/>
       <c r="P41" s="12"/>
     </row>
-    <row r="42" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B42" s="3">
         <v>61.212121212121403</v>
@@ -2576,9 +2576,9 @@
       <c r="O42" s="12"/>
       <c r="P42" s="12"/>
     </row>
-    <row r="43" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B43" s="3">
         <v>74.561972744971044</v>
@@ -2619,9 +2619,9 @@
       <c r="O43" s="12"/>
       <c r="P43" s="12"/>
     </row>
-    <row r="44" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B44" s="3">
         <v>77.203445990722642</v>
@@ -2662,9 +2662,9 @@
       <c r="O44" s="12"/>
       <c r="P44" s="12"/>
     </row>
-    <row r="45" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B45">
         <v>81.345769487008852</v>
@@ -2705,9 +2705,9 @@
       <c r="O45" s="12"/>
       <c r="P45" s="12"/>
     </row>
-    <row r="46" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B46">
         <v>86.81608437705998</v>
@@ -2748,9 +2748,9 @@
       <c r="O46" s="12"/>
       <c r="P46" s="12"/>
     </row>
-    <row r="47" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B47">
         <v>78.989898989899032</v>
@@ -2782,16 +2782,16 @@
         <v>0.97901488599056297</v>
       </c>
       <c r="L47" s="14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M47" s="12"/>
       <c r="N47" s="12"/>
       <c r="O47" s="12"/>
       <c r="P47" s="12"/>
     </row>
-    <row r="48" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B48">
         <v>91.919191919191647</v>
@@ -2832,9 +2832,9 @@
       <c r="O48" s="12"/>
       <c r="P48" s="12"/>
     </row>
-    <row r="49" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B49">
         <v>67.48834110592945</v>
@@ -2875,9 +2875,9 @@
       <c r="O49" s="12"/>
       <c r="P49" s="12"/>
     </row>
-    <row r="50" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B50">
         <v>90.939373750832701</v>
@@ -2918,9 +2918,9 @@
       <c r="O50" s="12"/>
       <c r="P50" s="12"/>
     </row>
-    <row r="51" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B51">
         <v>91.695501730103473</v>
@@ -2961,9 +2961,9 @@
       <c r="O51" s="12"/>
       <c r="P51" s="12"/>
     </row>
-    <row r="52" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B52">
         <v>80.622837370242479</v>
@@ -3004,9 +3004,9 @@
       <c r="O52" s="12"/>
       <c r="P52" s="12"/>
     </row>
-    <row r="53" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B53">
         <v>85.45454545454561</v>
@@ -3047,9 +3047,9 @@
       <c r="O53" s="12"/>
       <c r="P53" s="12"/>
     </row>
-    <row r="54" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54">
         <v>86.571981923821582</v>
@@ -3090,9 +3090,9 @@
       <c r="O54" s="12"/>
       <c r="P54" s="12"/>
     </row>
-    <row r="55" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55">
         <v>82.94470353097897</v>
@@ -3133,9 +3133,9 @@
       <c r="O55" s="12"/>
       <c r="P55" s="12"/>
     </row>
-    <row r="56" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B56">
         <v>54.254594962559629</v>
@@ -3176,9 +3176,9 @@
       <c r="O56" s="12"/>
       <c r="P56" s="12"/>
     </row>
-    <row r="57" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B57">
         <v>84.834123222749412</v>
@@ -3219,9 +3219,9 @@
       <c r="O57" s="12"/>
       <c r="P57" s="12"/>
     </row>
-    <row r="58" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B58">
         <v>83.21678321678263</v>
@@ -3262,9 +3262,9 @@
       <c r="O58" s="12"/>
       <c r="P58" s="12"/>
     </row>
-    <row r="59" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B59">
         <v>72.525252525252341</v>
@@ -3305,9 +3305,9 @@
       <c r="O59" s="12"/>
       <c r="P59" s="12"/>
     </row>
-    <row r="60" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B60">
         <v>92.99663299663321</v>
@@ -3348,9 +3348,9 @@
       <c r="O60" s="12"/>
       <c r="P60" s="12"/>
     </row>
-    <row r="61" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B61">
         <v>92.375765827093275</v>
@@ -3391,9 +3391,9 @@
       <c r="O61" s="12"/>
       <c r="P61" s="12"/>
     </row>
-    <row r="62" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B62">
         <v>93.429158110882724</v>
@@ -3434,9 +3434,9 @@
       <c r="O62" s="12"/>
       <c r="P62" s="12"/>
     </row>
-    <row r="63" spans="1:16" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B63">
         <v>94.074074074074119</v>
@@ -3477,9 +3477,9 @@
       <c r="O63" s="12"/>
       <c r="P63" s="12"/>
     </row>
-    <row r="64" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B64">
         <v>97.103548153512108</v>
@@ -3520,9 +3520,9 @@
       <c r="O64" s="12"/>
       <c r="P64" s="12"/>
     </row>
-    <row r="65" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B65">
         <v>93.244194229415683</v>
@@ -3563,9 +3563,9 @@
       <c r="O65" s="12"/>
       <c r="P65" s="12"/>
     </row>
-    <row r="66" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B66">
         <v>90.197413206262368</v>
@@ -3606,9 +3606,9 @@
       <c r="O66" s="12"/>
       <c r="P66" s="12"/>
     </row>
-    <row r="67" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B67">
         <v>71.600803750837144</v>
@@ -3649,9 +3649,9 @@
       <c r="O67" s="12"/>
       <c r="P67" s="12"/>
     </row>
-    <row r="68" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B68">
         <v>83.205038488452956</v>
@@ -3692,9 +3692,9 @@
       <c r="O68" s="12"/>
       <c r="P68" s="12"/>
     </row>
-    <row r="69" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B69">
         <v>53.792623521224613</v>
@@ -3735,9 +3735,9 @@
       <c r="O69" s="12"/>
       <c r="P69" s="12"/>
     </row>
-    <row r="70" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B70">
         <v>88.501026694045464</v>
@@ -3778,9 +3778,9 @@
       <c r="O70" s="12"/>
       <c r="P70" s="12"/>
     </row>
-    <row r="71" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B71" s="9">
         <v>84.583620096352305</v>
@@ -3821,9 +3821,9 @@
       <c r="O71" s="12"/>
       <c r="P71" s="12"/>
     </row>
-    <row r="72" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B72">
         <v>66.079582517939031</v>
@@ -3864,9 +3864,9 @@
       <c r="O72" s="12"/>
       <c r="P72" s="12"/>
     </row>
-    <row r="73" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B73">
         <v>72.376438727149363</v>
@@ -3907,9 +3907,9 @@
       <c r="O73" s="12"/>
       <c r="P73" s="12"/>
     </row>
-    <row r="74" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B74">
         <v>86.828919112383502</v>
@@ -3950,9 +3950,9 @@
       <c r="O74" s="12"/>
       <c r="P74" s="12"/>
     </row>
-    <row r="75" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B75">
         <v>79.96044825313065</v>
@@ -3993,9 +3993,9 @@
       <c r="O75" s="12"/>
       <c r="P75" s="12"/>
     </row>
-    <row r="76" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B76">
         <v>70.657439446366638</v>
@@ -4031,16 +4031,16 @@
         <v>2.0175647077458554</v>
       </c>
       <c r="L76" s="15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M76" s="12"/>
       <c r="N76" s="12"/>
       <c r="O76" s="12"/>
       <c r="P76" s="12"/>
     </row>
-    <row r="77" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B77">
         <v>83.389149363697101</v>
@@ -4081,9 +4081,9 @@
       <c r="O77" s="12"/>
       <c r="P77" s="12"/>
     </row>
-    <row r="78" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B78">
         <v>89.1542930923179</v>
@@ -4124,9 +4124,9 @@
       <c r="O78" s="12"/>
       <c r="P78" s="12"/>
     </row>
-    <row r="79" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B79">
         <v>66.426229508196755</v>
@@ -4167,9 +4167,9 @@
       <c r="O79" s="12"/>
       <c r="P79" s="12"/>
     </row>
-    <row r="80" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B80">
         <v>62.814719173660293</v>
@@ -4210,9 +4210,9 @@
       <c r="O80" s="12"/>
       <c r="P80" s="12"/>
     </row>
-    <row r="81" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B81">
         <v>86.360655737705315</v>
@@ -4253,7 +4253,7 @@
       <c r="O81" s="12"/>
       <c r="P81" s="12"/>
     </row>
-    <row r="82" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H82" s="12"/>
       <c r="I82" s="15"/>
       <c r="J82" s="15"/>
@@ -4264,7 +4264,7 @@
       <c r="O82" s="12"/>
       <c r="P82" s="12"/>
     </row>
-    <row r="83" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H83" s="12"/>
       <c r="I83" s="15"/>
       <c r="J83" s="15"/>
@@ -4275,7 +4275,7 @@
       <c r="O83" s="12"/>
       <c r="P83" s="12"/>
     </row>
-    <row r="84" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H84" s="12"/>
       <c r="I84" s="15"/>
       <c r="J84" s="15"/>
@@ -4286,7 +4286,7 @@
       <c r="O84" s="12"/>
       <c r="P84" s="12"/>
     </row>
-    <row r="85" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H85" s="12"/>
       <c r="I85" s="15"/>
       <c r="J85" s="15"/>
@@ -4297,7 +4297,7 @@
       <c r="O85" s="12"/>
       <c r="P85" s="12"/>
     </row>
-    <row r="86" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H86" s="12"/>
       <c r="I86" s="15"/>
       <c r="J86" s="15"/>
@@ -4308,7 +4308,7 @@
       <c r="O86" s="12"/>
       <c r="P86" s="12"/>
     </row>
-    <row r="87" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H87" s="12"/>
       <c r="I87" s="15"/>
       <c r="J87" s="15"/>
@@ -4319,7 +4319,7 @@
       <c r="O87" s="12"/>
       <c r="P87" s="12"/>
     </row>
-    <row r="88" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H88" s="12"/>
       <c r="I88" s="15"/>
       <c r="J88" s="15"/>
@@ -4330,7 +4330,7 @@
       <c r="O88" s="12"/>
       <c r="P88" s="12"/>
     </row>
-    <row r="89" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H89" s="12"/>
       <c r="I89" s="15"/>
       <c r="J89" s="15"/>
@@ -4341,7 +4341,7 @@
       <c r="O89" s="12"/>
       <c r="P89" s="12"/>
     </row>
-    <row r="90" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H90" s="12"/>
       <c r="I90" s="15"/>
       <c r="J90" s="15"/>
@@ -4352,7 +4352,7 @@
       <c r="O90" s="12"/>
       <c r="P90" s="12"/>
     </row>
-    <row r="91" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H91" s="12"/>
       <c r="I91" s="15"/>
       <c r="J91" s="15"/>
@@ -4363,7 +4363,7 @@
       <c r="O91" s="12"/>
       <c r="P91" s="12"/>
     </row>
-    <row r="92" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H92" s="12"/>
       <c r="I92" s="15"/>
       <c r="J92" s="15"/>
@@ -4374,7 +4374,7 @@
       <c r="O92" s="12"/>
       <c r="P92" s="12"/>
     </row>
-    <row r="93" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H93" s="12"/>
       <c r="I93" s="15"/>
       <c r="J93" s="15"/>
@@ -4385,7 +4385,7 @@
       <c r="O93" s="12"/>
       <c r="P93" s="12"/>
     </row>
-    <row r="94" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H94" s="12"/>
       <c r="I94" s="15"/>
       <c r="J94" s="15"/>
@@ -4396,7 +4396,7 @@
       <c r="O94" s="12"/>
       <c r="P94" s="12"/>
     </row>
-    <row r="95" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H95" s="12"/>
       <c r="I95" s="15"/>
       <c r="J95" s="15"/>
@@ -4407,7 +4407,7 @@
       <c r="O95" s="12"/>
       <c r="P95" s="12"/>
     </row>
-    <row r="96" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H96" s="12"/>
       <c r="I96" s="15"/>
       <c r="J96" s="15"/>
@@ -4418,7 +4418,7 @@
       <c r="O96" s="12"/>
       <c r="P96" s="12"/>
     </row>
-    <row r="97" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H97" s="12"/>
       <c r="I97" s="15"/>
       <c r="J97" s="15"/>
@@ -4429,7 +4429,7 @@
       <c r="O97" s="12"/>
       <c r="P97" s="12"/>
     </row>
-    <row r="98" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H98" s="12"/>
       <c r="I98" s="15"/>
       <c r="J98" s="15"/>
@@ -4440,7 +4440,7 @@
       <c r="O98" s="12"/>
       <c r="P98" s="12"/>
     </row>
-    <row r="99" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H99" s="12"/>
       <c r="I99" s="15"/>
       <c r="J99" s="15"/>
@@ -4452,7 +4452,7 @@
       <c r="P99" s="15"/>
       <c r="Q99" s="9"/>
     </row>
-    <row r="100" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H100" s="12"/>
       <c r="I100" s="15"/>
       <c r="J100" s="15"/>
@@ -4464,7 +4464,7 @@
       <c r="P100" s="15"/>
       <c r="Q100" s="9"/>
     </row>
-    <row r="101" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H101" s="12"/>
       <c r="I101" s="12"/>
       <c r="J101" s="15"/>
@@ -4476,7 +4476,7 @@
       <c r="P101" s="15"/>
       <c r="Q101" s="9"/>
     </row>
-    <row r="102" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H102" s="12"/>
       <c r="I102" s="12"/>
       <c r="J102" s="15"/>
@@ -4488,7 +4488,7 @@
       <c r="P102" s="15"/>
       <c r="Q102" s="9"/>
     </row>
-    <row r="103" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H103" s="12"/>
       <c r="I103" s="12"/>
       <c r="J103" s="15"/>
@@ -4500,7 +4500,7 @@
       <c r="P103" s="15"/>
       <c r="Q103" s="9"/>
     </row>
-    <row r="104" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H104" s="12"/>
       <c r="I104" s="12"/>
       <c r="J104" s="15"/>
@@ -4512,7 +4512,7 @@
       <c r="P104" s="15"/>
       <c r="Q104" s="9"/>
     </row>
-    <row r="105" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H105" s="12"/>
       <c r="I105" s="12"/>
       <c r="J105" s="15"/>
@@ -4524,7 +4524,7 @@
       <c r="P105" s="15"/>
       <c r="Q105" s="9"/>
     </row>
-    <row r="106" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
       <c r="J106" s="15"/>
@@ -4536,7 +4536,7 @@
       <c r="P106" s="15"/>
       <c r="Q106" s="9"/>
     </row>
-    <row r="107" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
       <c r="J107" s="15"/>
@@ -4548,7 +4548,7 @@
       <c r="P107" s="15"/>
       <c r="Q107" s="9"/>
     </row>
-    <row r="108" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
       <c r="J108" s="15"/>
@@ -4560,7 +4560,7 @@
       <c r="P108" s="15"/>
       <c r="Q108" s="9"/>
     </row>
-    <row r="109" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H109" s="12"/>
       <c r="I109" s="12"/>
       <c r="J109" s="15"/>
@@ -4572,7 +4572,7 @@
       <c r="P109" s="15"/>
       <c r="Q109" s="9"/>
     </row>
-    <row r="110" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H110" s="12"/>
       <c r="I110" s="12"/>
       <c r="J110" s="15"/>
@@ -4584,7 +4584,7 @@
       <c r="P110" s="15"/>
       <c r="Q110" s="9"/>
     </row>
-    <row r="111" spans="8:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H111" s="12"/>
       <c r="I111" s="12"/>
       <c r="J111" s="15"/>
@@ -4596,7 +4596,7 @@
       <c r="P111" s="15"/>
       <c r="Q111" s="9"/>
     </row>
-    <row r="112" spans="8:17" x14ac:dyDescent="0.35">
+    <row r="112" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H112" s="12"/>
       <c r="I112" s="12"/>
       <c r="J112" s="15"/>
@@ -4608,7 +4608,7 @@
       <c r="P112" s="15"/>
       <c r="Q112" s="9"/>
     </row>
-    <row r="113" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="113" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J113" s="9"/>
       <c r="K113" s="9"/>
       <c r="L113" s="9"/>
@@ -4618,7 +4618,7 @@
       <c r="P113" s="9"/>
       <c r="Q113" s="9"/>
     </row>
-    <row r="114" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="114" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J114" s="9"/>
       <c r="K114" s="9"/>
       <c r="L114" s="9"/>
@@ -4628,7 +4628,7 @@
       <c r="P114" s="9"/>
       <c r="Q114" s="9"/>
     </row>
-    <row r="115" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="115" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J115" s="9"/>
       <c r="K115" s="9"/>
       <c r="L115" s="9"/>
@@ -4638,7 +4638,7 @@
       <c r="P115" s="9"/>
       <c r="Q115" s="9"/>
     </row>
-    <row r="116" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="116" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J116" s="9"/>
       <c r="K116" s="9"/>
       <c r="L116" s="9"/>
@@ -4648,7 +4648,7 @@
       <c r="P116" s="9"/>
       <c r="Q116" s="9"/>
     </row>
-    <row r="117" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="117" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J117" s="9"/>
       <c r="K117" s="9"/>
       <c r="L117" s="9"/>
@@ -4658,7 +4658,7 @@
       <c r="P117" s="9"/>
       <c r="Q117" s="9"/>
     </row>
-    <row r="118" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="118" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J118" s="9"/>
       <c r="K118" s="9"/>
       <c r="L118" s="9"/>
@@ -4668,7 +4668,7 @@
       <c r="P118" s="9"/>
       <c r="Q118" s="9"/>
     </row>
-    <row r="119" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="119" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J119" s="9"/>
       <c r="K119" s="9"/>
       <c r="L119" s="9"/>
@@ -4678,7 +4678,7 @@
       <c r="P119" s="9"/>
       <c r="Q119" s="9"/>
     </row>
-    <row r="120" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="120" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J120" s="9"/>
       <c r="K120" s="9"/>
       <c r="L120" s="9"/>
@@ -4688,7 +4688,7 @@
       <c r="P120" s="9"/>
       <c r="Q120" s="9"/>
     </row>
-    <row r="121" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="121" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J121" s="9"/>
       <c r="K121" s="9"/>
       <c r="L121" s="9"/>
@@ -4698,7 +4698,7 @@
       <c r="P121" s="9"/>
       <c r="Q121" s="9"/>
     </row>
-    <row r="122" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="122" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J122" s="9"/>
       <c r="K122" s="9"/>
       <c r="L122" s="9"/>
@@ -4708,7 +4708,7 @@
       <c r="P122" s="9"/>
       <c r="Q122" s="9"/>
     </row>
-    <row r="123" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="123" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J123" s="9"/>
       <c r="K123" s="9"/>
       <c r="L123" s="9"/>
@@ -4718,7 +4718,7 @@
       <c r="P123" s="9"/>
       <c r="Q123" s="9"/>
     </row>
-    <row r="124" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="124" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J124" s="9"/>
       <c r="K124" s="9"/>
       <c r="L124" s="9"/>
@@ -4728,7 +4728,7 @@
       <c r="P124" s="9"/>
       <c r="Q124" s="9"/>
     </row>
-    <row r="125" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="125" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J125" s="9"/>
       <c r="K125" s="9"/>
       <c r="L125" s="9"/>
@@ -4738,7 +4738,7 @@
       <c r="P125" s="9"/>
       <c r="Q125" s="9"/>
     </row>
-    <row r="126" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="126" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J126" s="9"/>
       <c r="K126" s="9"/>
       <c r="L126" s="9"/>
@@ -4748,7 +4748,7 @@
       <c r="P126" s="9"/>
       <c r="Q126" s="9"/>
     </row>
-    <row r="127" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="127" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J127" s="9"/>
       <c r="K127" s="9"/>
       <c r="L127" s="9"/>
@@ -4758,7 +4758,7 @@
       <c r="P127" s="9"/>
       <c r="Q127" s="9"/>
     </row>
-    <row r="128" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="128" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J128" s="9"/>
       <c r="K128" s="9"/>
       <c r="L128" s="9"/>
@@ -4768,7 +4768,7 @@
       <c r="P128" s="9"/>
       <c r="Q128" s="9"/>
     </row>
-    <row r="129" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="129" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J129" s="9"/>
       <c r="K129" s="9"/>
       <c r="L129" s="9"/>
@@ -4778,7 +4778,7 @@
       <c r="P129" s="9"/>
       <c r="Q129" s="9"/>
     </row>
-    <row r="130" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="130" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J130" s="9"/>
       <c r="K130" s="9"/>
       <c r="L130" s="9"/>
@@ -4788,7 +4788,7 @@
       <c r="P130" s="9"/>
       <c r="Q130" s="9"/>
     </row>
-    <row r="131" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="131" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J131" s="9"/>
       <c r="K131" s="9"/>
       <c r="L131" s="9"/>
@@ -4798,7 +4798,7 @@
       <c r="P131" s="9"/>
       <c r="Q131" s="9"/>
     </row>
-    <row r="132" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="132" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J132" s="9"/>
       <c r="K132" s="9"/>
       <c r="L132" s="9"/>
@@ -4808,7 +4808,7 @@
       <c r="P132" s="9"/>
       <c r="Q132" s="9"/>
     </row>
-    <row r="133" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="133" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J133" s="9"/>
       <c r="K133" s="9"/>
       <c r="L133" s="9"/>
@@ -4818,7 +4818,7 @@
       <c r="P133" s="9"/>
       <c r="Q133" s="9"/>
     </row>
-    <row r="134" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="134" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J134" s="9"/>
       <c r="K134" s="9"/>
       <c r="L134" s="9"/>
@@ -4828,7 +4828,7 @@
       <c r="P134" s="9"/>
       <c r="Q134" s="9"/>
     </row>
-    <row r="135" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="135" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J135" s="9"/>
       <c r="K135" s="9"/>
       <c r="L135" s="9"/>
@@ -4838,7 +4838,7 @@
       <c r="P135" s="9"/>
       <c r="Q135" s="9"/>
     </row>
-    <row r="136" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="136" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J136" s="9"/>
       <c r="K136" s="9"/>
       <c r="L136" s="9"/>
@@ -4848,7 +4848,7 @@
       <c r="P136" s="9"/>
       <c r="Q136" s="9"/>
     </row>
-    <row r="137" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="137" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J137" s="9"/>
       <c r="K137" s="9"/>
       <c r="L137" s="9"/>
@@ -4858,7 +4858,7 @@
       <c r="P137" s="9"/>
       <c r="Q137" s="9"/>
     </row>
-    <row r="138" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="138" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J138" s="9"/>
       <c r="K138" s="9"/>
       <c r="L138" s="9"/>
@@ -4868,7 +4868,7 @@
       <c r="P138" s="9"/>
       <c r="Q138" s="9"/>
     </row>
-    <row r="139" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="139" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J139" s="9"/>
       <c r="K139" s="9"/>
       <c r="L139" s="9"/>
@@ -4878,7 +4878,7 @@
       <c r="P139" s="9"/>
       <c r="Q139" s="9"/>
     </row>
-    <row r="140" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="140" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J140" s="9"/>
       <c r="K140" s="9"/>
       <c r="L140" s="9"/>
@@ -4888,7 +4888,7 @@
       <c r="P140" s="9"/>
       <c r="Q140" s="9"/>
     </row>
-    <row r="141" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="141" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J141" s="9"/>
       <c r="K141" s="9"/>
       <c r="L141" s="9"/>
@@ -4898,7 +4898,7 @@
       <c r="P141" s="9"/>
       <c r="Q141" s="9"/>
     </row>
-    <row r="142" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="142" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J142" s="9"/>
       <c r="K142" s="9"/>
       <c r="L142" s="9"/>
@@ -4908,7 +4908,7 @@
       <c r="P142" s="9"/>
       <c r="Q142" s="9"/>
     </row>
-    <row r="143" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="143" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J143" s="9"/>
       <c r="K143" s="9"/>
       <c r="L143" s="9"/>
@@ -4918,7 +4918,7 @@
       <c r="P143" s="9"/>
       <c r="Q143" s="9"/>
     </row>
-    <row r="144" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="144" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J144" s="9"/>
       <c r="K144" s="9"/>
       <c r="L144" s="9"/>
@@ -4928,7 +4928,7 @@
       <c r="P144" s="9"/>
       <c r="Q144" s="9"/>
     </row>
-    <row r="145" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="145" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J145" s="9"/>
       <c r="K145" s="9"/>
       <c r="L145" s="9"/>
@@ -4938,7 +4938,7 @@
       <c r="P145" s="9"/>
       <c r="Q145" s="9"/>
     </row>
-    <row r="146" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="146" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J146" s="9"/>
       <c r="K146" s="9"/>
       <c r="L146" s="9"/>
@@ -4948,7 +4948,7 @@
       <c r="P146" s="9"/>
       <c r="Q146" s="9"/>
     </row>
-    <row r="147" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="147" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J147" s="9"/>
       <c r="K147" s="9"/>
       <c r="L147" s="9"/>
@@ -4958,7 +4958,7 @@
       <c r="P147" s="9"/>
       <c r="Q147" s="9"/>
     </row>
-    <row r="148" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="148" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J148" s="9"/>
       <c r="K148" s="9"/>
       <c r="L148" s="9"/>
@@ -4968,7 +4968,7 @@
       <c r="P148" s="9"/>
       <c r="Q148" s="9"/>
     </row>
-    <row r="149" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="149" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J149" s="9"/>
       <c r="K149" s="9"/>
       <c r="L149" s="9"/>
@@ -4978,7 +4978,7 @@
       <c r="P149" s="9"/>
       <c r="Q149" s="9"/>
     </row>
-    <row r="150" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="150" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J150" s="9"/>
       <c r="K150" s="9"/>
       <c r="L150" s="9"/>
@@ -4988,7 +4988,7 @@
       <c r="P150" s="9"/>
       <c r="Q150" s="9"/>
     </row>
-    <row r="151" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="151" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J151" s="9"/>
       <c r="K151" s="9"/>
       <c r="L151" s="9"/>
@@ -4998,7 +4998,7 @@
       <c r="P151" s="9"/>
       <c r="Q151" s="9"/>
     </row>
-    <row r="152" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="152" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J152" s="9"/>
       <c r="K152" s="9"/>
       <c r="L152" s="9"/>
@@ -5008,7 +5008,7 @@
       <c r="P152" s="9"/>
       <c r="Q152" s="9"/>
     </row>
-    <row r="153" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="153" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J153" s="9"/>
       <c r="K153" s="9"/>
       <c r="L153" s="9"/>
@@ -5018,7 +5018,7 @@
       <c r="P153" s="9"/>
       <c r="Q153" s="9"/>
     </row>
-    <row r="154" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="154" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J154" s="9"/>
       <c r="K154" s="9"/>
       <c r="L154" s="9"/>
@@ -5028,7 +5028,7 @@
       <c r="P154" s="9"/>
       <c r="Q154" s="9"/>
     </row>
-    <row r="155" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="155" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J155" s="9"/>
       <c r="K155" s="9"/>
       <c r="L155" s="9"/>
@@ -5038,7 +5038,7 @@
       <c r="P155" s="9"/>
       <c r="Q155" s="9"/>
     </row>
-    <row r="156" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="156" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J156" s="9"/>
       <c r="K156" s="9"/>
       <c r="L156" s="9"/>
@@ -5048,7 +5048,7 @@
       <c r="P156" s="9"/>
       <c r="Q156" s="9"/>
     </row>
-    <row r="157" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="157" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J157" s="9"/>
       <c r="K157" s="9"/>
       <c r="L157" s="9"/>
@@ -5058,7 +5058,7 @@
       <c r="P157" s="9"/>
       <c r="Q157" s="9"/>
     </row>
-    <row r="158" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="158" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J158" s="9"/>
       <c r="K158" s="9"/>
       <c r="L158" s="9"/>
@@ -5068,7 +5068,7 @@
       <c r="P158" s="9"/>
       <c r="Q158" s="9"/>
     </row>
-    <row r="159" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="159" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J159" s="9"/>
       <c r="K159" s="9"/>
       <c r="L159" s="9"/>
@@ -5078,7 +5078,7 @@
       <c r="P159" s="9"/>
       <c r="Q159" s="9"/>
     </row>
-    <row r="160" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="160" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J160" s="9"/>
       <c r="K160" s="9"/>
       <c r="L160" s="9"/>
@@ -5088,7 +5088,7 @@
       <c r="P160" s="9"/>
       <c r="Q160" s="9"/>
     </row>
-    <row r="161" spans="10:17" x14ac:dyDescent="0.35">
+    <row r="161" spans="10:17" x14ac:dyDescent="0.25">
       <c r="J161" s="9"/>
       <c r="K161" s="9"/>
       <c r="L161" s="9"/>
